--- a/artfynd/A 44363-2023 artfynd.xlsx
+++ b/artfynd/A 44363-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44363-2023 artfynd.xlsx
+++ b/artfynd/A 44363-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112628480</v>
+        <v>112670190</v>
       </c>
       <c r="B2" t="n">
-        <v>73978</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>313148</v>
+        <v>313198</v>
       </c>
       <c r="R2" t="n">
-        <v>6524999</v>
+        <v>6525007</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112628481</v>
+        <v>112628477</v>
       </c>
       <c r="B3" t="n">
-        <v>73978</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313150</v>
+        <v>313198</v>
       </c>
       <c r="R3" t="n">
-        <v>6525047</v>
+        <v>6525007</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,17 +871,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,12 +902,7 @@
         <v>112628482</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112628477</v>
+        <v>116374368</v>
       </c>
       <c r="B5" t="n">
-        <v>94594</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NV om Bredmossen, Dls</t>
+          <t>Bön, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313197</v>
+        <v>313144</v>
       </c>
       <c r="R5" t="n">
-        <v>6525007</v>
+        <v>6525044</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,46 +1077,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112628478</v>
+        <v>112782978</v>
       </c>
       <c r="B6" t="n">
-        <v>73978</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,34 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NV om Bredmossen, Dls</t>
+          <t>NO om Bredmossen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313188</v>
+        <v>313181</v>
       </c>
       <c r="R6" t="n">
-        <v>6525003</v>
+        <v>6525034</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,21 +1174,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1245,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112670190</v>
+        <v>112628478</v>
       </c>
       <c r="B7" t="n">
-        <v>94580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313197</v>
+        <v>313187</v>
       </c>
       <c r="R7" t="n">
-        <v>6525007</v>
+        <v>6525002</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,17 +1274,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1362,50 +1302,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112782978</v>
+        <v>112628480</v>
       </c>
       <c r="B8" t="n">
-        <v>91158</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NO om Bredmossen, Dls</t>
+          <t>NV om Bredmossen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313181</v>
+        <v>313149</v>
       </c>
       <c r="R8" t="n">
-        <v>6525034</v>
+        <v>6524999</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,6 +1383,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1464,53 +1414,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116374368</v>
+        <v>112628481</v>
       </c>
       <c r="B9" t="n">
-        <v>94174</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bön, Dls</t>
+          <t>NV om Bredmossen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313144</v>
+        <v>313150</v>
       </c>
       <c r="R9" t="n">
-        <v>6525044</v>
+        <v>6525048</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,12 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,31 +1495,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116374382</v>
+        <v>116374387</v>
       </c>
       <c r="B10" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313236</v>
+        <v>313150</v>
       </c>
       <c r="R10" t="n">
-        <v>6525028</v>
+        <v>6525052</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-04-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,19 +1623,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116374383</v>
+        <v>116374381</v>
       </c>
       <c r="B11" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1713,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313144</v>
+        <v>313344</v>
       </c>
       <c r="R11" t="n">
-        <v>6525044</v>
+        <v>6525045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,19 +1725,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116374381</v>
+        <v>116374382</v>
       </c>
       <c r="B12" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1820,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313344</v>
+        <v>313236</v>
       </c>
       <c r="R12" t="n">
-        <v>6525045</v>
+        <v>6525028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,6 +1824,108 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>116374383</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bön, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>313144</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6525044</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44363-2023 artfynd.xlsx
+++ b/artfynd/A 44363-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112670190</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112628477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112628482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116374368</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112782978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112628478</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112628480</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112628481</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116374387</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116374381</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116374382</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,8 +1986,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116374383</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>